--- a/june 2026/LMT_JUNE_26/Clinix.xlsx
+++ b/june 2026/LMT_JUNE_26/Clinix.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034602EA-A63D-4B73-86F1-C0C2ED9D94CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6371D50-DA86-456B-9AB1-EFEE7A7016BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3328,7 +3328,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -3356,7 +3356,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -4549,7 +4549,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -4577,7 +4577,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -5770,7 +5770,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -5798,7 +5798,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -6991,7 +6991,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -7019,7 +7019,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -8212,7 +8212,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -8240,7 +8240,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -9433,7 +9433,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -9461,7 +9461,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -10651,7 +10651,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -10679,7 +10679,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -11868,7 +11868,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -11896,7 +11896,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -13085,7 +13085,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -13113,7 +13113,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -14302,7 +14302,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -14330,7 +14330,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -18269,7 +18269,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -18297,7 +18297,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -19486,7 +19486,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -19514,7 +19514,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -20703,7 +20703,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -20731,7 +20731,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -21920,7 +21920,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -21948,7 +21948,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -23142,7 +23142,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -23170,7 +23170,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -23381,7 +23381,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>121979.79672029999</v>
+        <v>113170.11324929999</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23615,11 +23615,11 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18</f>
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>12591</v>
+        <v>4197</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18</f>
@@ -23627,27 +23627,27 @@
       </c>
       <c r="K18" s="171">
         <f>+'1'!K18+'2'!K18+'4'!K18+'3'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18</f>
-        <v>440.68500000000006</v>
+        <v>146.89500000000001</v>
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>1007.28</v>
+        <v>335.76</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>11143.035</v>
+        <v>3714.3450000000003</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>2005.7462999999998</v>
+        <v>668.58209999999997</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>65.743906499999994</v>
+        <v>21.914635499999999</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>13214.525206499999</v>
+        <v>4404.8417355000001</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -24093,11 +24093,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>3840</v>
+        <v>3680</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>252303.3</v>
+        <v>243909.3</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24105,27 +24105,27 @@
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
-        <v>8830.6155000000017</v>
+        <v>8536.8255000000008</v>
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>20184.263999999999</v>
+        <v>19512.743999999999</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>223288.42050000001</v>
+        <v>215859.73050000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>40191.915689999994</v>
+        <v>38854.751489999995</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>1317.4016809499999</v>
+        <v>1273.5724099499998</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>264797.73787095002</v>
+        <v>255988.05439995002</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="U26" s="164">
         <f>SUM(U14:U25)</f>
-        <v>264797.73787095002</v>
+        <v>255988.05439994999</v>
       </c>
     </row>
     <row r="27" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24190,7 +24190,7 @@
       <c r="O28" s="239"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>252303.3</v>
+        <v>243909.3</v>
       </c>
     </row>
     <row r="29" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24211,7 +24211,7 @@
       <c r="O29" s="241"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>20184.263999999999</v>
+        <v>19512.743999999999</v>
       </c>
     </row>
     <row r="30" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24232,7 +24232,7 @@
       <c r="O30" s="241"/>
       <c r="P30" s="153">
         <f>K25</f>
-        <v>8830.6155000000017</v>
+        <v>8536.8255000000008</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24254,7 +24254,7 @@
       <c r="O31" s="241"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>223288.42049999998</v>
+        <v>215859.73049999998</v>
       </c>
     </row>
     <row r="32" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24279,7 +24279,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>40191.915689999994</v>
+        <v>38854.751489999995</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24301,7 +24301,7 @@
       <c r="O33" s="243"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>263480.33618999994</v>
+        <v>254714.48198999997</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>6587.0084047499986</v>
+        <v>6367.8620497499996</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24336,7 +24336,7 @@
       <c r="O35" s="221"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>270067.34459474997</v>
+        <v>261082.34403974997</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24440,21 +24440,22 @@
   <dimension ref="A2:XFD37"/>
   <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.453125" customWidth="1"/>
-    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.453125" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10" style="69" customWidth="1"/>
-    <col min="15" max="15" width="9.54296875" customWidth="1"/>
-    <col min="16" max="16" width="9.26953125" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7265625" style="69" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="4.54296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
@@ -24507,8 +24508,7 @@
       <c r="L4" s="202"/>
       <c r="M4" s="202"/>
       <c r="N4" s="203">
-        <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46183</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -24535,8 +24535,8 @@
       <c r="L5" s="202"/>
       <c r="M5" s="202"/>
       <c r="N5" s="203">
-        <f ca="1">N4-1</f>
-        <v>46205</v>
+        <f>N4-1</f>
+        <v>46182</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -24955,36 +24955,36 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="114">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="3"/>
-        <v>12591</v>
+        <v>4197</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="103">
         <f t="shared" si="4"/>
-        <v>440.68500000000006</v>
+        <v>146.89500000000001</v>
       </c>
       <c r="L18" s="104">
         <f t="shared" si="5"/>
-        <v>1007.28</v>
+        <v>335.76</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="6"/>
-        <v>11143.035</v>
+        <v>3714.3450000000003</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>2005.7462999999998</v>
+        <v>668.58209999999997</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="1"/>
-        <v>65.743906499999994</v>
+        <v>21.914635499999999</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="2"/>
-        <v>13214.525206499999</v>
+        <v>4404.8417355000001</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25344,36 +25344,36 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>1800</v>
+        <v>1640</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>116224.2</v>
+        <v>107830.2</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
         <f t="shared" si="9"/>
-        <v>4067.8470000000002</v>
+        <v>3774.0570000000002</v>
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>9297.9360000000015</v>
+        <v>8626.4160000000011</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>102858.41699999999</v>
+        <v>95429.726999999984</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>18514.515059999998</v>
+        <v>17177.350859999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>606.86466029999997</v>
+        <v>563.03538929999991</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>121979.79672029999</v>
+        <v>113170.11324929999</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25384,10 +25384,7 @@
       <c r="E26" s="144"/>
       <c r="F26" s="144"/>
       <c r="G26" s="145"/>
-      <c r="H26" s="145">
-        <f>H25/40</f>
-        <v>45</v>
-      </c>
+      <c r="H26" s="145"/>
       <c r="I26" s="146"/>
       <c r="K26" s="147"/>
       <c r="L26" s="147"/>
@@ -25426,7 +25423,7 @@
       <c r="O28" s="239"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>116224.2</v>
+        <v>107830.2</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25447,7 +25444,7 @@
       <c r="O29" s="241"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>9297.9360000000015</v>
+        <v>8626.4160000000011</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25468,7 +25465,7 @@
       <c r="O30" s="241"/>
       <c r="P30" s="153">
         <f>K25</f>
-        <v>4067.8470000000002</v>
+        <v>3774.0570000000002</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25490,7 +25487,7 @@
       <c r="O31" s="241"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>102858.417</v>
+        <v>95429.726999999999</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25515,7 +25512,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>18514.515059999998</v>
+        <v>17177.350859999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25537,7 +25534,7 @@
       <c r="O33" s="243"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>121372.93205999999</v>
+        <v>112607.07785999999</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25562,7 +25559,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>606.86466029999997</v>
+        <v>563.03538930000002</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25572,7 +25569,7 @@
       <c r="O35" s="221"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>121979.79672029999</v>
+        <v>113170.11324929999</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25652,7 +25649,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -25689,8 +25686,8 @@
     <col min="12" max="12" width="8.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.81640625" style="69" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="6.36328125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -25729,7 +25726,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:20 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20 16383:16384" x14ac:dyDescent="0.35">
       <c r="A4" s="201" t="s">
         <v>94</v>
       </c>
@@ -25743,8 +25740,7 @@
       <c r="L4" s="202"/>
       <c r="M4" s="202"/>
       <c r="N4" s="203">
-        <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -25771,8 +25767,8 @@
       <c r="L5" s="202"/>
       <c r="M5" s="202"/>
       <c r="N5" s="203">
-        <f ca="1">N4-1</f>
-        <v>46205</v>
+        <f>N4-1</f>
+        <v>46196</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -27034,7 +27030,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -27062,7 +27058,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -28264,7 +28260,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -28292,7 +28288,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -29485,7 +29481,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -29513,7 +29509,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -30706,7 +30702,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -30734,7 +30730,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
